--- a/docs/evidence/20261023_持有成本口徑差_A段/20261023_持有成本口徑差_A段.xlsx
+++ b/docs/evidence/20261023_持有成本口徑差_A段/20261023_持有成本口徑差_A段.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="640">
   <si>
     <r>
       <rPr>
@@ -3348,7 +3348,83 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">數</t>
+      <t xml:space="preserve">數（總成本 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">總 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小時；非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$/hr </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">直接加權 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.729</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -7008,6 +7084,46 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">欄；與規格一致，世代實際未揭露）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">GB200 </t>
     </r>
     <r>
@@ -10543,7 +10659,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">是上界：</t>
+      <t xml:space="preserve">是下界：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">85% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">是公司對專案 </t>
     </r>
     <r>
       <rPr>
@@ -10562,7 +10697,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">率是公司對專案的估計，實際可能更低（營運費更高）。</t>
+      <t xml:space="preserve">率的估計（偏樂觀的上限），實際營運費用可能更高。</t>
     </r>
   </si>
   <si>
@@ -10987,6 +11122,169 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廠房取 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）所需殘值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.31%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.9 $B/GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">6%</t>
   </si>
   <si>
@@ -20117,7 +20415,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">隱含營運費用（≤</t>
+      <t xml:space="preserve">隱含營運費用（≥</t>
     </r>
     <r>
       <rPr>
@@ -20136,7 +20434,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）低於 </t>
+      <t xml:space="preserve">，下界）低於 </t>
     </r>
     <r>
       <rPr>
@@ -22777,6 +23075,10 @@
         <f aca="false">FLOOR(F7*(1-F8)*1000/F12,1)</f>
         <v>4052</v>
       </c>
+      <c r="G34" s="19" t="n">
+        <f aca="false">SUMPRODUCT($C$6:$F$6,C34:F34)</f>
+        <v>16251</v>
+      </c>
       <c r="H34" s="8" t="s">
         <v>99</v>
       </c>
@@ -25239,23 +25541,23 @@
         <v>8</v>
       </c>
       <c r="L14" s="27" t="s">
-        <v>229</v>
+        <v>292</v>
       </c>
       <c r="M14" s="29" t="n">
-        <f aca="false">'TK 拆解'!G66</f>
-        <v>9.35311859805586</v>
+        <f aca="false">'TK 拆解'!F66</f>
+        <v>12.2254710045841</v>
       </c>
       <c r="N14" s="29" t="n">
         <f aca="false">I14/M14</f>
-        <v>0.855329686684704</v>
+        <v>0.654371516402132</v>
       </c>
       <c r="O14" s="29" t="n">
         <f aca="false">J14/M14</f>
-        <v>0.71277473890392</v>
+        <v>0.545309597001777</v>
       </c>
       <c r="P14" s="29" t="n">
         <f aca="false">K14/M14</f>
-        <v>0.855329686684704</v>
+        <v>0.654371516402132</v>
       </c>
       <c r="Q14" s="30" t="s">
         <v>219</v>
@@ -25276,13 +25578,13 @@
         <v>286</v>
       </c>
       <c r="W14" s="27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="X14" s="27" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y14" s="30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z14" s="27" t="s">
         <v>281</v>
@@ -25290,7 +25592,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -25320,16 +25622,16 @@
     </row>
     <row r="16" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C16" s="28" t="n">
         <v>16.3</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E16" s="28" t="n">
         <v>1</v>
@@ -25338,7 +25640,7 @@
         <v>1.25</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H16" s="29" t="n">
         <f aca="false">C16/E16</f>
@@ -25376,42 +25678,42 @@
         <v>1.74273423662009</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R16" s="30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S16" s="30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="T16" s="30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U16" s="30" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V16" s="30" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="W16" s="27" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="X16" s="27" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Y16" s="30" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z16" s="27" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C17" s="28" t="n">
         <v>16.3</v>
@@ -25426,7 +25728,7 @@
         <v>1.12780698259266</v>
       </c>
       <c r="G17" s="30" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H17" s="29" t="n">
         <f aca="false">C17/E17</f>
@@ -25464,48 +25766,48 @@
         <v>1.54524157370776</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="R17" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S17" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="T17" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="U17" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="V17" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="W17" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X17" s="27" t="s">
         <v>16</v>
       </c>
       <c r="Y17" s="30" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Z17" s="27" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C18" s="28" t="n">
         <v>15.9</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E18" s="28" t="n">
         <v>1</v>
@@ -25514,7 +25816,7 @@
         <v>0.421</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H18" s="29" t="n">
         <f aca="false">C18/E18</f>
@@ -25533,7 +25835,7 @@
         <v>37.7672209026128</v>
       </c>
       <c r="L18" s="27" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M18" s="29" t="n">
         <f aca="false">'TK 拆解'!D48</f>
@@ -25552,39 +25854,39 @@
         <v>1.02949548236061</v>
       </c>
       <c r="Q18" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="R18" s="30" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="S18" s="30" t="s">
         <v>219</v>
       </c>
       <c r="T18" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="U18" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="V18" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="W18" s="27" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="X18" s="27" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y18" s="30" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z18" s="27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -25614,10 +25916,10 @@
     </row>
     <row r="20" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C20" s="28" t="n">
         <v>2.53</v>
@@ -25633,7 +25935,7 @@
         <v>0.000718048</v>
       </c>
       <c r="G20" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H20" s="29" t="n">
         <f aca="false">C20*E20*F20</f>
@@ -25652,7 +25954,7 @@
         <v>15.9139542144</v>
       </c>
       <c r="L20" s="27" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M20" s="29" t="n">
         <f aca="false">'TK 拆解'!C66</f>
@@ -25671,40 +25973,40 @@
         <v>1.64009183316048</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R20" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S20" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T20" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="U20" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="V20" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W20" s="27"/>
       <c r="X20" s="27" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y20" s="30" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z20" s="27" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C21" s="28" t="n">
         <v>3.15</v>
@@ -25720,7 +26022,7 @@
         <v>0.000718048</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H21" s="29" t="n">
         <f aca="false">C21*E21*F21</f>
@@ -25739,7 +26041,7 @@
         <v>19.813816512</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M21" s="29" t="n">
         <f aca="false">'TK 拆解'!C66</f>
@@ -25758,40 +26060,40 @@
         <v>2.04201157093103</v>
       </c>
       <c r="Q21" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R21" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S21" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T21" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="U21" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="V21" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W21" s="27"/>
       <c r="X21" s="27" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y21" s="30" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z21" s="27" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C22" s="28" t="n">
         <v>6.16</v>
@@ -25807,7 +26109,7 @@
         <v>0.000718048</v>
       </c>
       <c r="G22" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H22" s="29" t="n">
         <f aca="false">C22*E22*F22</f>
@@ -25826,7 +26128,7 @@
         <v>38.7470189568</v>
       </c>
       <c r="L22" s="27" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M22" s="29" t="n">
         <f aca="false">'TK 拆解'!C66</f>
@@ -25845,40 +26147,40 @@
         <v>3.99326707204291</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R22" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S22" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T22" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="U22" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="V22" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W22" s="27"/>
       <c r="X22" s="27" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Y22" s="30" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Z22" s="27" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C23" s="28" t="n">
         <v>3.29</v>
@@ -25894,7 +26196,7 @@
         <v>0.000718048</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H23" s="29" t="n">
         <f aca="false">C23*E23*F23</f>
@@ -25913,7 +26215,7 @@
         <v>20.6944305792</v>
       </c>
       <c r="L23" s="27" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M23" s="29" t="n">
         <f aca="false">'TK 拆解'!C66</f>
@@ -25932,40 +26234,40 @@
         <v>2.13276764075019</v>
       </c>
       <c r="Q23" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R23" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S23" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T23" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="U23" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="V23" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W23" s="27"/>
       <c r="X23" s="27" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Y23" s="30" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Z23" s="27" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C24" s="28" t="n">
         <v>10.5</v>
@@ -25981,7 +26283,7 @@
         <v>0.000501768</v>
       </c>
       <c r="G24" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H24" s="29" t="n">
         <f aca="false">C24*E24*F24</f>
@@ -26000,7 +26302,7 @@
         <v>46.15262064</v>
       </c>
       <c r="L24" s="27" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M24" s="29" t="n">
         <f aca="false">'TK 拆解'!D66</f>
@@ -26019,40 +26321,40 @@
         <v>5.22788344816701</v>
       </c>
       <c r="Q24" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R24" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S24" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T24" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="U24" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="V24" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W24" s="27"/>
       <c r="X24" s="27" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Y24" s="30" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z24" s="27" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C25" s="28" t="n">
         <v>5</v>
@@ -26068,7 +26370,7 @@
         <v>0.000501768</v>
       </c>
       <c r="G25" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">C25*E25*F25</f>
@@ -26087,7 +26389,7 @@
         <v>21.9774384</v>
       </c>
       <c r="L25" s="27" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M25" s="29" t="n">
         <f aca="false">'TK 拆解'!D66</f>
@@ -26106,43 +26408,44 @@
         <v>2.48946830865096</v>
       </c>
       <c r="Q25" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R25" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S25" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T25" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="U25" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="V25" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W25" s="27"/>
       <c r="X25" s="27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y25" s="30" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z25" s="27" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="C26" s="28" t="n">
-        <v>2.7222</v>
+        <v>356</v>
+      </c>
+      <c r="C26" s="27" t="n">
+        <f aca="false">6200000000/5/52000/8760</f>
+        <v>2.72216368106779</v>
       </c>
       <c r="D26" s="27" t="s">
         <v>168</v>
@@ -26155,23 +26458,23 @@
         <v>0.000487008</v>
       </c>
       <c r="G26" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">C26*E26*F26</f>
-        <v>11.613422635776</v>
+        <v>11.6132676923077</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">H26*1</f>
-        <v>11.613422635776</v>
+        <v>11.6132676923077</v>
       </c>
       <c r="J26" s="29" t="n">
         <f aca="false">H26*0.7</f>
-        <v>8.1293958450432</v>
+        <v>8.12928738461539</v>
       </c>
       <c r="K26" s="29" t="n">
         <f aca="false">H26*1</f>
-        <v>11.613422635776</v>
+        <v>11.6132676923077</v>
       </c>
       <c r="L26" s="27" t="s">
         <v>215</v>
@@ -26182,51 +26485,51 @@
       </c>
       <c r="N26" s="29" t="n">
         <f aca="false">I26/M26</f>
-        <v>1.06678157140356</v>
+        <v>1.06676733866255</v>
       </c>
       <c r="O26" s="29" t="n">
         <f aca="false">J26/M26</f>
-        <v>0.746747099982494</v>
+        <v>0.746737137063788</v>
       </c>
       <c r="P26" s="29" t="n">
         <f aca="false">K26/M26</f>
-        <v>1.06678157140356</v>
+        <v>1.06676733866255</v>
       </c>
       <c r="Q26" s="30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="R26" s="30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="S26" s="30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="T26" s="30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U26" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="V26" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W26" s="27"/>
       <c r="X26" s="27" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Y26" s="30" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Z26" s="27" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C27" s="28" t="n">
         <v>7.15</v>
@@ -26242,7 +26545,7 @@
         <v>0.000487008</v>
       </c>
       <c r="G27" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">C27*E27*F27</f>
@@ -26280,42 +26583,42 @@
         <v>2.80195732699121</v>
       </c>
       <c r="Q27" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R27" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S27" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T27" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="U27" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="V27" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W27" s="27"/>
       <c r="X27" s="27" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Y27" s="30" t="s">
         <v>195</v>
       </c>
       <c r="Z27" s="27" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -26346,12 +26649,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -26366,19 +26669,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -26389,7 +26692,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">'TK 拆解'!E66</f>
@@ -26410,7 +26713,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">'TK 拆解'!E39</f>
@@ -26429,15 +26732,15 @@
         <v>0.899581179818709</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">'TK 拆解'!E46</f>
@@ -26455,18 +26758,18 @@
         <v>1.18389897395422</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">'TK 拆解'!E47</f>
@@ -26487,7 +26790,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">'TK 拆解'!E65</f>
@@ -26506,18 +26809,18 @@
         <v>0.733871911435009</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>287</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'TK 拆解'!E50+'TK 拆解'!E54</f>
@@ -26536,7 +26839,7 @@
         <v>0.926011596093138</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>16</v>
@@ -26544,7 +26847,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D11" s="11" t="n">
         <f aca="false">C9-B9</f>
@@ -26555,12 +26858,12 @@
         <v>0.444731894938738</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D12" s="11" t="n">
         <f aca="false">C10-B10</f>
@@ -26573,7 +26876,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D13" s="23" t="n">
         <f aca="false">D11+D12-D5</f>
@@ -26582,7 +26885,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -26594,30 +26897,30 @@
     </row>
     <row r="16" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B17" s="11" t="n">
         <f aca="false">$C$10*(1-(1+G17)^(-5))/G17</f>
@@ -26636,15 +26939,18 @@
         <v>0.175780857690022</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0.0331</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B18" s="11" t="n">
         <f aca="false">$C$10*(1-(1+G18)^(-5))/G18</f>
@@ -26668,7 +26974,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">$C$10*(1-(1+G19)^(-5))/G19</f>
@@ -26692,7 +26998,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">$C$10*(1-(1+G20)^(-5))/G20</f>
@@ -26711,7 +27017,7 @@
         <v>0.466497511363636</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0.1</v>
@@ -26719,7 +27025,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">$C$10*(1-(1+G21)^(-5))/G21</f>
@@ -26743,7 +27049,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B22" s="24" t="n">
         <v>0.0616740150304683</v>
@@ -26758,12 +27064,12 @@
         <v>0.0423379998661479</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -26775,33 +27081,33 @@
     </row>
     <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B25" s="11" t="n">
         <f aca="false">外部價格換算!I7</f>
@@ -26820,18 +27126,18 @@
         <v>0.933734907964136</v>
       </c>
       <c r="F25" s="30" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G25" s="30" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B26" s="11" t="n">
         <f aca="false">外部價格換算!I9</f>
@@ -26850,18 +27156,18 @@
         <v>1.06554859978662</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G26" s="30" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H26" s="30" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B27" s="11" t="n">
         <f aca="false">外部價格換算!I10</f>
@@ -26880,18 +27186,18 @@
         <v>1.83715275825279</v>
       </c>
       <c r="F27" s="30" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G27" s="30" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H27" s="30" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B28" s="11" t="n">
         <f aca="false">外部價格換算!I12</f>
@@ -26910,18 +27216,18 @@
         <v>1.30874303280426</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G28" s="30" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H28" s="30" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B29" s="11" t="n">
         <f aca="false">外部價格換算!I13</f>
@@ -26940,18 +27246,18 @@
         <v>1.09061919400355</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H29" s="30" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B30" s="11" t="n">
         <f aca="false">外部價格換算!I17</f>
@@ -26970,18 +27276,18 @@
         <v>1.54524157370776</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G30" s="30" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H30" s="27" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B31" s="11" t="n">
         <f aca="false">外部價格換算!I20</f>
@@ -27000,22 +27306,22 @@
         <v>1.64009183316048</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G31" s="30" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B32" s="11" t="n">
         <f aca="false">外部價格換算!I26</f>
-        <v>11.613422635776</v>
+        <v>11.6132676923077</v>
       </c>
       <c r="C32" s="11" t="n">
         <f aca="false">'TK 拆解'!E66</f>
@@ -27023,25 +27329,25 @@
       </c>
       <c r="D32" s="11" t="n">
         <f aca="false">B32-C32</f>
-        <v>0.727011633665944</v>
+        <v>0.726856690197637</v>
       </c>
       <c r="E32" s="11" t="n">
         <f aca="false">B32/C32</f>
-        <v>1.06678157140356</v>
+        <v>1.06676733866255</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G32" s="27" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H32" s="27" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -27053,25 +27359,25 @@
     </row>
     <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>11</v>
@@ -27079,7 +27385,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B36" s="11" t="n">
         <f aca="false">外部價格換算!I6</f>
@@ -27106,12 +27412,12 @@
         <v>1.0370872451052</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B37" s="11" t="n">
         <f aca="false">外部價格換算!I12</f>
@@ -27138,12 +27444,12 @@
         <v>1.71065937336941</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B38" s="11" t="n">
         <f aca="false">外部價格換算!I13</f>
@@ -27172,7 +27478,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B39" s="11" t="n">
         <f aca="false">外部價格換算!I16</f>
@@ -27199,12 +27505,12 @@
         <v>1.39418738929607</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B40" s="11" t="n">
         <f aca="false">外部價格換算!I17</f>
@@ -27233,7 +27539,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B41" s="11" t="n">
         <f aca="false">外部價格換算!I7</f>
@@ -27262,7 +27568,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -27274,7 +27580,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>195</v>
@@ -27283,10 +27589,10 @@
         <v>196</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>11</v>
@@ -27294,7 +27600,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B45" s="11" t="n">
         <f aca="false">MIN(外部價格換算!N6,外部價格換算!N7)</f>
@@ -27305,18 +27611,18 @@
         <v>1.12048188955696</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B46" s="11" t="n">
         <f aca="false">MIN(外部價格換算!N12,外部價格換算!N13)</f>
@@ -27327,15 +27633,15 @@
         <v>1.30874303280426</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B47" s="11" t="n">
         <f aca="false">外部價格換算!O20</f>
@@ -27346,18 +27652,18 @@
         <v>2.04201157093103</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B48" s="11" t="n">
         <f aca="false">外部價格換算!N10</f>
@@ -27368,15 +27674,15 @@
         <v>4.59288189563197</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B49" s="11" t="n">
         <f aca="false">MIN(外部價格換算!N17,外部價格換算!N16)</f>
@@ -27387,13 +27693,13 @@
         <v>1.54524157370776</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -27431,152 +27737,152 @@
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>287</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27584,25 +27890,25 @@
         <v>253</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>287</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27610,25 +27916,25 @@
         <v>264</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27636,285 +27942,285 @@
         <v>281</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>287</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G15" s="30" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="H15" s="30" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
+        <v>585</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>586</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>587</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>583</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="F17" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="G17" s="30" t="s">
         <v>584</v>
       </c>
-      <c r="C17" s="30" t="s">
-        <v>585</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>581</v>
-      </c>
-      <c r="F17" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="G17" s="30" t="s">
-        <v>582</v>
-      </c>
       <c r="H17" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G18" s="30" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
+        <v>593</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>594</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>595</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="E19" s="27" t="s">
         <v>591</v>
       </c>
-      <c r="B19" s="30" t="s">
-        <v>592</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>593</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>589</v>
-      </c>
       <c r="F19" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -27945,22 +28251,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27968,19 +28274,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27988,19 +28294,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28008,19 +28314,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28028,19 +28334,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C5" s="30" t="s">
+        <v>618</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>619</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>620</v>
+      </c>
+      <c r="F5" s="30" t="s">
         <v>616</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>617</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>618</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28048,19 +28354,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28068,19 +28374,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28088,19 +28394,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28108,19 +28414,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
